--- a/Rotation-3-Thermodynamics/Sample-Data/FreezingPointDepression_SampleData.xlsx
+++ b/Rotation-3-Thermodynamics/Sample-Data/FreezingPointDepression_SampleData.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prajay\Documents\GitHub\CHE-3131\Rotation-3-Thermodynamics\Sample-Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338C4A0A-F45A-48DB-9619-552098F99122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EAEA25-FDA7-40D5-A76E-DC8EAB589FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pure" sheetId="3" r:id="rId1"/>
-    <sheet name="Mixture1" sheetId="4" r:id="rId2"/>
-    <sheet name="Mixture2" sheetId="5" r:id="rId3"/>
+    <sheet name="Mix1" sheetId="4" r:id="rId2"/>
+    <sheet name="Mix2" sheetId="5" r:id="rId3"/>
     <sheet name="Data" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -41,19 +41,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
   <si>
-    <t>Mixture2</t>
-  </si>
-  <si>
     <t>Time</t>
   </si>
   <si>
     <t>Temperature</t>
   </si>
   <si>
-    <t>Mixture1</t>
+    <t>Mass (g)</t>
   </si>
   <si>
-    <t>Mass (g)</t>
+    <t>Mix1</t>
+  </si>
+  <si>
+    <t>Mix2</t>
   </si>
 </sst>
 </file>
@@ -327,10 +327,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -7476,10 +7476,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -15469,10 +15469,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -24575,7 +24575,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -24588,7 +24588,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0.21299999999999999</v>

--- a/Rotation-3-Thermodynamics/Sample-Data/FreezingPointDepression_SampleData.xlsx
+++ b/Rotation-3-Thermodynamics/Sample-Data/FreezingPointDepression_SampleData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofdallas-my.sharepoint.com/personal/pmpatel_udallas_edu/Documents/OneDrive - University of Dallas/Documents/GitHub/CHE-3131/Rotation-3-Thermodynamics/Sample-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="13_ncr:1_{B2EAEA25-FDA7-40D5-A76E-DC8EAB589FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80055877-444F-4474-8E54-0D3A896419F1}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{B2EAEA25-FDA7-40D5-A76E-DC8EAB589FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0528165-4BD7-460A-833C-D95832106A47}"/>
   <bookViews>
-    <workbookView xWindow="36120" yWindow="1980" windowWidth="23040" windowHeight="12105" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36120" yWindow="1980" windowWidth="23040" windowHeight="12105" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pure" sheetId="3" r:id="rId1"/>
@@ -96,6 +96,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="0.000"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -143,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -154,6 +157,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -171,6 +177,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24707,9 +24717,10 @@
         <v>5.32</v>
       </c>
       <c r="D4" s="2">
-        <v>-1.69</v>
-      </c>
-      <c r="E4" s="2">
+        <f>C4-C2</f>
+        <v>-1.6899999999999995</v>
+      </c>
+      <c r="E4" s="6">
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="F4" s="2">
